--- a/10_ToMONGOLICA/04_Admixture/subSTRCombMed_RMnotes.xlsx
+++ b/10_ToMONGOLICA/04_Admixture/subSTRCombMed_RMnotes.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmohn\Documents\GitHub\QMacGs\10_ToMONGOLICA\04_Admixture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92ABFE15-2225-42FD-A825-36082444A8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C492BF-9734-4801-AD8D-9F700D6C1945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9772" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3420" yWindow="2760" windowWidth="12351" windowHeight="6891" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="subSTRCombMed_RMnotes" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">subSTRCombMed_RMnotes!$A$1:$AL$700</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">subSTRCombMed_RMnotes!$A$1:$AR$701</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -7187,6 +7187,12 @@
       <c r="AL14" t="s">
         <v>328</v>
       </c>
+      <c r="AM14" s="2"/>
+      <c r="AN14" s="2"/>
+      <c r="AO14" s="2"/>
+      <c r="AP14" s="2"/>
+      <c r="AQ14" s="2"/>
+      <c r="AR14" s="2"/>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A15">
@@ -24124,7 +24130,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="161" spans="1:38" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A161">
         <v>697</v>
       </c>
@@ -24240,7 +24246,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="162" spans="1:38" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A162">
         <v>698</v>
       </c>
@@ -24356,7 +24362,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="163" spans="1:38" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A163">
         <v>699</v>
       </c>
@@ -24472,7 +24478,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="164" spans="1:38" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A164">
         <v>689</v>
       </c>
@@ -24588,7 +24594,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="165" spans="1:38" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A165">
         <v>332</v>
       </c>
@@ -24704,7 +24710,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="166" spans="1:38" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A166">
         <v>333</v>
       </c>
@@ -24820,7 +24826,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="167" spans="1:38" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A167">
         <v>334</v>
       </c>
@@ -24936,7 +24942,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="168" spans="1:38" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A168">
         <v>335</v>
       </c>
@@ -25052,7 +25058,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="169" spans="1:38" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A169">
         <v>336</v>
       </c>
@@ -25168,7 +25174,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="170" spans="1:38" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A170">
         <v>337</v>
       </c>
@@ -25284,7 +25290,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="171" spans="1:38" s="2" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A171" s="2">
         <v>338</v>
       </c>
@@ -25399,8 +25405,14 @@
       <c r="AL171" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="AM171"/>
+      <c r="AN171"/>
+      <c r="AO171"/>
+      <c r="AP171"/>
+      <c r="AQ171"/>
+      <c r="AR171"/>
     </row>
-    <row r="172" spans="1:38" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A172">
         <v>339</v>
       </c>
@@ -25516,7 +25528,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="173" spans="1:38" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A173">
         <v>340</v>
       </c>
@@ -25632,7 +25644,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="174" spans="1:38" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A174">
         <v>341</v>
       </c>
@@ -25748,7 +25760,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="175" spans="1:38" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A175">
         <v>342</v>
       </c>
@@ -25864,7 +25876,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="176" spans="1:38" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:44" x14ac:dyDescent="0.4">
       <c r="A176">
         <v>343</v>
       </c>
@@ -84794,10 +84806,10 @@
     </row>
     <row r="684" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A684">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B684" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C684" s="1">
         <v>1.0000000000000001E-5</v>
@@ -84839,43 +84851,43 @@
         <v>0</v>
       </c>
       <c r="P684" s="1">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="Q684" s="1">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="R684">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="S684" s="1">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="T684" s="1">
+        <v>2.0999999999999999E-5</v>
+      </c>
+      <c r="U684" s="1">
+        <v>1.4E-5</v>
+      </c>
+      <c r="V684" s="1">
+        <v>1.5999999999999999E-5</v>
+      </c>
+      <c r="W684" s="1">
         <v>2.3E-5</v>
       </c>
-      <c r="Q684" s="1">
+      <c r="X684" s="1">
+        <v>1.8E-5</v>
+      </c>
+      <c r="Y684" s="1">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Z684" s="1">
+        <v>1.7E-5</v>
+      </c>
+      <c r="AA684" s="1">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="AB684" s="1">
         <v>2.6999999999999999E-5</v>
-      </c>
-      <c r="R684">
-        <v>0.99989099999999997</v>
-      </c>
-      <c r="S684" s="1">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="T684" s="1">
-        <v>2.3E-5</v>
-      </c>
-      <c r="U684" s="1">
-        <v>1.5E-5</v>
-      </c>
-      <c r="V684" s="1">
-        <v>1.2999999999999999E-5</v>
-      </c>
-      <c r="W684" s="1">
-        <v>2.1999999999999999E-5</v>
-      </c>
-      <c r="X684" s="1">
-        <v>1.5999999999999999E-5</v>
-      </c>
-      <c r="Y684" s="1">
-        <v>1.9000000000000001E-5</v>
-      </c>
-      <c r="Z684" s="1">
-        <v>1.9000000000000001E-5</v>
-      </c>
-      <c r="AA684" s="1">
-        <v>1.2E-5</v>
-      </c>
-      <c r="AB684" s="1">
-        <v>2.9E-5</v>
       </c>
       <c r="AD684" t="s">
         <v>325</v>
@@ -84901,10 +84913,10 @@
     </row>
     <row r="685" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A685">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B685" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C685" s="1">
         <v>1.0000000000000001E-5</v>
@@ -84913,7 +84925,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="E685">
-        <v>0.99988999999999995</v>
+        <v>0.999888</v>
       </c>
       <c r="F685" s="1">
         <v>1.0000000000000001E-5</v>
@@ -84946,43 +84958,43 @@
         <v>0</v>
       </c>
       <c r="P685" s="1">
-        <v>2.4000000000000001E-5</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="Q685" s="1">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="R685">
-        <v>0.99989700000000004</v>
+        <v>0.99989300000000003</v>
       </c>
       <c r="S685" s="1">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="T685" s="1">
-        <v>2.8E-5</v>
+        <v>2.0999999999999999E-5</v>
       </c>
       <c r="U685" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.8E-5</v>
       </c>
       <c r="V685" s="1">
-        <v>1.8E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="W685" s="1">
         <v>2.0999999999999999E-5</v>
       </c>
       <c r="X685" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.8E-5</v>
       </c>
       <c r="Y685" s="1">
-        <v>1.2E-5</v>
+        <v>1.5999999999999999E-5</v>
       </c>
       <c r="Z685" s="1">
-        <v>1.9000000000000001E-5</v>
+        <v>1.5999999999999999E-5</v>
       </c>
       <c r="AA685" s="1">
-        <v>1.9000000000000001E-5</v>
+        <v>1.4E-5</v>
       </c>
       <c r="AB685" s="1">
-        <v>3.8000000000000002E-5</v>
+        <v>3.0000000000000001E-5</v>
       </c>
       <c r="AD685" t="s">
         <v>325</v>
@@ -85008,10 +85020,10 @@
     </row>
     <row r="686" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A686">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B686" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C686" s="1">
         <v>1.0000000000000001E-5</v>
@@ -85053,43 +85065,43 @@
         <v>0</v>
       </c>
       <c r="P686" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>2.3E-5</v>
       </c>
       <c r="Q686" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>2.6999999999999999E-5</v>
       </c>
       <c r="R686">
-        <v>0.99990000000000001</v>
+        <v>0.99989099999999997</v>
       </c>
       <c r="S686" s="1">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="T686" s="1">
-        <v>2.0999999999999999E-5</v>
+        <v>2.3E-5</v>
       </c>
       <c r="U686" s="1">
-        <v>1.4E-5</v>
+        <v>1.5E-5</v>
       </c>
       <c r="V686" s="1">
+        <v>1.2999999999999999E-5</v>
+      </c>
+      <c r="W686" s="1">
+        <v>2.1999999999999999E-5</v>
+      </c>
+      <c r="X686" s="1">
         <v>1.5999999999999999E-5</v>
       </c>
-      <c r="W686" s="1">
-        <v>2.3E-5</v>
-      </c>
-      <c r="X686" s="1">
-        <v>1.8E-5</v>
-      </c>
       <c r="Y686" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.9000000000000001E-5</v>
       </c>
       <c r="Z686" s="1">
-        <v>1.7E-5</v>
+        <v>1.9000000000000001E-5</v>
       </c>
       <c r="AA686" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.2E-5</v>
       </c>
       <c r="AB686" s="1">
-        <v>2.6999999999999999E-5</v>
+        <v>2.9E-5</v>
       </c>
       <c r="AD686" t="s">
         <v>325</v>
@@ -85115,10 +85127,10 @@
     </row>
     <row r="687" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A687">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B687" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C687" s="1">
         <v>1.0000000000000001E-5</v>
@@ -85127,7 +85139,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="E687">
-        <v>0.999888</v>
+        <v>0.99988999999999995</v>
       </c>
       <c r="F687" s="1">
         <v>1.0000000000000001E-5</v>
@@ -85166,37 +85178,37 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="R687">
-        <v>0.99989300000000003</v>
+        <v>0.99990000000000001</v>
       </c>
       <c r="S687" s="1">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="T687" s="1">
-        <v>2.0999999999999999E-5</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="U687" s="1">
-        <v>1.8E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="V687" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.4E-5</v>
       </c>
       <c r="W687" s="1">
-        <v>2.0999999999999999E-5</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="X687" s="1">
-        <v>1.8E-5</v>
+        <v>1.5999999999999999E-5</v>
       </c>
       <c r="Y687" s="1">
-        <v>1.5999999999999999E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="Z687" s="1">
-        <v>1.5999999999999999E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="AA687" s="1">
-        <v>1.4E-5</v>
+        <v>1.5E-5</v>
       </c>
       <c r="AB687" s="1">
-        <v>3.0000000000000001E-5</v>
+        <v>2.5000000000000001E-5</v>
       </c>
       <c r="AD687" t="s">
         <v>325</v>
@@ -85222,10 +85234,10 @@
     </row>
     <row r="688" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A688">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B688" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C688" s="1">
         <v>1.0000000000000001E-5</v>
@@ -85279,31 +85291,31 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="T688" s="1">
-        <v>2.8E-5</v>
+        <v>2.4000000000000001E-5</v>
       </c>
       <c r="U688" s="1">
+        <v>1.9000000000000001E-5</v>
+      </c>
+      <c r="V688" s="1">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="W688" s="1">
+        <v>2.3E-5</v>
+      </c>
+      <c r="X688" s="1">
+        <v>1.4E-5</v>
+      </c>
+      <c r="Y688" s="1">
+        <v>1.2E-5</v>
+      </c>
+      <c r="Z688" s="1">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="AA688" s="1">
         <v>1.1E-5</v>
       </c>
-      <c r="V688" s="1">
-        <v>1.5E-5</v>
-      </c>
-      <c r="W688" s="1">
-        <v>2.5999999999999998E-5</v>
-      </c>
-      <c r="X688" s="1">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Y688" s="1">
-        <v>1.4E-5</v>
-      </c>
-      <c r="Z688" s="1">
-        <v>1.4E-5</v>
-      </c>
-      <c r="AA688" s="1">
-        <v>1.2E-5</v>
-      </c>
       <c r="AB688" s="1">
-        <v>2.1999999999999999E-5</v>
+        <v>2.0999999999999999E-5</v>
       </c>
       <c r="AD688" t="s">
         <v>325</v>
@@ -85329,10 +85341,10 @@
     </row>
     <row r="689" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A689">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B689" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C689" s="1">
         <v>1.0000000000000001E-5</v>
@@ -85374,43 +85386,43 @@
         <v>0</v>
       </c>
       <c r="P689" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>2.1999999999999999E-5</v>
       </c>
       <c r="Q689" s="1">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="R689">
-        <v>0.99989899999999998</v>
+        <v>0.99990000000000001</v>
       </c>
       <c r="S689" s="1">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="T689" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>2.8E-5</v>
       </c>
       <c r="U689" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.1E-5</v>
       </c>
       <c r="V689" s="1">
+        <v>1.1E-5</v>
+      </c>
+      <c r="W689" s="1">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="X689" s="1">
         <v>1.4E-5</v>
       </c>
-      <c r="W689" s="1">
-        <v>2.4000000000000001E-5</v>
-      </c>
-      <c r="X689" s="1">
-        <v>1.0000000000000001E-5</v>
-      </c>
       <c r="Y689" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="Z689" s="1">
-        <v>1.2999999999999999E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="AA689" s="1">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="AB689" s="1">
-        <v>2.3E-5</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="AD689" t="s">
         <v>325</v>
@@ -85436,10 +85448,10 @@
     </row>
     <row r="690" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A690">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B690" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="C690" s="1">
         <v>1.0000000000000001E-5</v>
@@ -85493,31 +85505,31 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="T690" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>2.8E-5</v>
       </c>
       <c r="U690" s="1">
-        <v>1.2E-5</v>
+        <v>1.4E-5</v>
       </c>
       <c r="V690" s="1">
-        <v>1.7E-5</v>
+        <v>1.9000000000000001E-5</v>
       </c>
       <c r="W690" s="1">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="X690" s="1">
+        <v>1.4E-5</v>
+      </c>
+      <c r="Y690" s="1">
         <v>1.2999999999999999E-5</v>
       </c>
-      <c r="Y690" s="1">
-        <v>1.4E-5</v>
-      </c>
       <c r="Z690" s="1">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="AA690" s="1">
-        <v>1.2E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="AB690" s="1">
-        <v>2.1999999999999999E-5</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="AD690" t="s">
         <v>325</v>
@@ -85543,10 +85555,10 @@
     </row>
     <row r="691" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A691">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B691" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="C691" s="1">
         <v>1.0000000000000001E-5</v>
@@ -85603,28 +85615,28 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="U691" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.2E-5</v>
       </c>
       <c r="V691" s="1">
+        <v>1.7E-5</v>
+      </c>
+      <c r="W691" s="1">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="X691" s="1">
+        <v>1.2999999999999999E-5</v>
+      </c>
+      <c r="Y691" s="1">
         <v>1.4E-5</v>
       </c>
-      <c r="W691" s="1">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="X691" s="1">
-        <v>1.5999999999999999E-5</v>
-      </c>
-      <c r="Y691" s="1">
-        <v>1.0000000000000001E-5</v>
-      </c>
       <c r="Z691" s="1">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="AA691" s="1">
-        <v>1.5E-5</v>
+        <v>1.2E-5</v>
       </c>
       <c r="AB691" s="1">
-        <v>2.5000000000000001E-5</v>
+        <v>2.1999999999999999E-5</v>
       </c>
       <c r="AD691" t="s">
         <v>325</v>
@@ -85650,10 +85662,10 @@
     </row>
     <row r="692" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A692">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B692" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C692" s="1">
         <v>1.0000000000000001E-5</v>
@@ -85710,28 +85722,28 @@
         <v>2.4000000000000001E-5</v>
       </c>
       <c r="U692" s="1">
-        <v>1.9000000000000001E-5</v>
+        <v>1.2E-5</v>
       </c>
       <c r="V692" s="1">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="W692" s="1">
-        <v>2.3E-5</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="X692" s="1">
-        <v>1.4E-5</v>
+        <v>1.2999999999999999E-5</v>
       </c>
       <c r="Y692" s="1">
-        <v>1.2E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="Z692" s="1">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="AA692" s="1">
-        <v>1.1E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="AB692" s="1">
-        <v>2.0999999999999999E-5</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="AD692" t="s">
         <v>325</v>
@@ -85757,10 +85769,10 @@
     </row>
     <row r="693" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A693">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B693" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C693" s="1">
         <v>1.0000000000000001E-5</v>
@@ -85802,7 +85814,7 @@
         <v>0</v>
       </c>
       <c r="P693" s="1">
-        <v>2.1999999999999999E-5</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="Q693" s="1">
         <v>2.0000000000000002E-5</v>
@@ -85814,31 +85826,31 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="T693" s="1">
-        <v>2.8E-5</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="U693" s="1">
-        <v>1.1E-5</v>
+        <v>1.2999999999999999E-5</v>
       </c>
       <c r="V693" s="1">
-        <v>1.1E-5</v>
-      </c>
-      <c r="W693" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="W693">
+        <v>6.5399999999999996E-4</v>
       </c>
       <c r="X693" s="1">
-        <v>1.4E-5</v>
+        <v>1.2E-5</v>
       </c>
       <c r="Y693" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="Z693" s="1">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="AA693" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.2999999999999999E-5</v>
       </c>
       <c r="AB693" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>2.3E-5</v>
       </c>
       <c r="AD693" t="s">
         <v>325</v>
@@ -85864,10 +85876,10 @@
     </row>
     <row r="694" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A694">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B694" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C694" s="1">
         <v>1.0000000000000001E-5</v>
@@ -85921,22 +85933,22 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="T694" s="1">
-        <v>2.4000000000000001E-5</v>
+        <v>2.3E-5</v>
       </c>
       <c r="U694" s="1">
-        <v>1.2E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="V694" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.5999999999999999E-5</v>
       </c>
       <c r="W694" s="1">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="X694" s="1">
+        <v>1.1E-5</v>
+      </c>
+      <c r="Y694" s="1">
         <v>1.2999999999999999E-5</v>
-      </c>
-      <c r="Y694" s="1">
-        <v>1.0000000000000001E-5</v>
       </c>
       <c r="Z694" s="1">
         <v>1.0000000000000001E-5</v>
@@ -85971,10 +85983,10 @@
     </row>
     <row r="695" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A695">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B695" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C695" s="1">
         <v>1.0000000000000001E-5</v>
@@ -86016,13 +86028,13 @@
         <v>0</v>
       </c>
       <c r="P695" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>2.4000000000000001E-5</v>
       </c>
       <c r="Q695" s="1">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="R695">
-        <v>0.99990000000000001</v>
+        <v>0.99989700000000004</v>
       </c>
       <c r="S695" s="1">
         <v>2.0000000000000002E-5</v>
@@ -86031,28 +86043,28 @@
         <v>2.8E-5</v>
       </c>
       <c r="U695" s="1">
-        <v>1.4E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="V695" s="1">
+        <v>1.8E-5</v>
+      </c>
+      <c r="W695" s="1">
+        <v>2.0999999999999999E-5</v>
+      </c>
+      <c r="X695" s="1">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Y695" s="1">
+        <v>1.2E-5</v>
+      </c>
+      <c r="Z695" s="1">
         <v>1.9000000000000001E-5</v>
       </c>
-      <c r="W695" s="1">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="X695" s="1">
-        <v>1.4E-5</v>
-      </c>
-      <c r="Y695" s="1">
-        <v>1.2999999999999999E-5</v>
-      </c>
-      <c r="Z695" s="1">
-        <v>1.0000000000000001E-5</v>
-      </c>
       <c r="AA695" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.9000000000000001E-5</v>
       </c>
       <c r="AB695" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>3.8000000000000002E-5</v>
       </c>
       <c r="AD695" t="s">
         <v>325</v>
@@ -86078,10 +86090,10 @@
     </row>
     <row r="696" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A696">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B696" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C696" s="1">
         <v>1.0000000000000001E-5</v>
@@ -86135,31 +86147,31 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="T696" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>2.8E-5</v>
       </c>
       <c r="U696" s="1">
-        <v>1.2999999999999999E-5</v>
+        <v>1.1E-5</v>
       </c>
       <c r="V696" s="1">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="W696">
-        <v>6.5399999999999996E-4</v>
+        <v>1.5E-5</v>
+      </c>
+      <c r="W696" s="1">
+        <v>2.5999999999999998E-5</v>
       </c>
       <c r="X696" s="1">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Y696" s="1">
+        <v>1.4E-5</v>
+      </c>
+      <c r="Z696" s="1">
+        <v>1.4E-5</v>
+      </c>
+      <c r="AA696" s="1">
         <v>1.2E-5</v>
       </c>
-      <c r="Y696" s="1">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Z696" s="1">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="AA696" s="1">
-        <v>1.2999999999999999E-5</v>
-      </c>
       <c r="AB696" s="1">
-        <v>2.3E-5</v>
+        <v>2.1999999999999999E-5</v>
       </c>
       <c r="AD696" t="s">
         <v>325</v>
@@ -86185,10 +86197,10 @@
     </row>
     <row r="697" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A697">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B697" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="C697" s="1">
         <v>1.0000000000000001E-5</v>
@@ -86236,7 +86248,7 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="R697">
-        <v>0.99990000000000001</v>
+        <v>0.99989899999999998</v>
       </c>
       <c r="S697" s="1">
         <v>2.0000000000000002E-5</v>
@@ -86245,28 +86257,28 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="U697" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="V697" s="1">
-        <v>1.7E-5</v>
+        <v>1.4E-5</v>
       </c>
       <c r="W697" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>2.4000000000000001E-5</v>
       </c>
       <c r="X697" s="1">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="Y697" s="1">
-        <v>1.8E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="Z697" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.2999999999999999E-5</v>
       </c>
       <c r="AA697" s="1">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="AB697" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>2.3E-5</v>
       </c>
       <c r="AD697" t="s">
         <v>325</v>
@@ -86292,10 +86304,10 @@
     </row>
     <row r="698" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A698">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B698" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C698" s="1">
         <v>1.0000000000000001E-5</v>
@@ -86349,22 +86361,22 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="T698" s="1">
-        <v>2.3E-5</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="U698" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="V698" s="1">
-        <v>1.5999999999999999E-5</v>
+        <v>1.7E-5</v>
       </c>
       <c r="W698" s="1">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="X698" s="1">
-        <v>1.1E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="Y698" s="1">
-        <v>1.2999999999999999E-5</v>
+        <v>1.8E-5</v>
       </c>
       <c r="Z698" s="1">
         <v>1.0000000000000001E-5</v>
@@ -86612,9 +86624,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL700" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AL700">
-      <sortCondition ref="AC1:AC700"/>
+  <autoFilter ref="A1:AR701" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AR701">
+      <sortCondition ref="AC1:AC701"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="X1:X1048576">
